--- a/data/Protologue_table_methanotrophs.xlsx
+++ b/data/Protologue_table_methanotrophs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aaudk-my.sharepoint.com/personal/vj52ou_bio_aau_dk/Documents/PhD/Methanotrophy_DK_paper/Naming/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aaudk-my.sharepoint.com/personal/vj52ou_bio_aau_dk/Documents/PhD/Methanotrophy_DK_paper/MFD_methanotrophs_DK/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{45C9EE7B-7875-4031-B53F-BE6B8D4737CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C36C033B-359D-4A47-A832-BE333EEBC5EA}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="8_{45C9EE7B-7875-4031-B53F-BE6B8D4737CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D7C076E-03E2-4E2A-B865-8A57694B7131}"/>
   <bookViews>
-    <workbookView xWindow="-29475" yWindow="0" windowWidth="17250" windowHeight="9945" xr2:uid="{CCCCBD59-4898-4DD4-97D0-E07D85E6C4DF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CCCCBD59-4898-4DD4-97D0-E07D85E6C4DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="155">
   <si>
     <t>Species name</t>
   </si>
@@ -336,39 +336,21 @@
     <t>59.44</t>
   </si>
   <si>
-    <t>GCA_963764725</t>
-  </si>
-  <si>
     <t>60.49</t>
   </si>
   <si>
-    <t>GCA_963706215</t>
-  </si>
-  <si>
     <t>63.9</t>
   </si>
   <si>
-    <t>GCA_963717565</t>
-  </si>
-  <si>
     <t>63.34</t>
   </si>
   <si>
-    <t>GCA_963706255</t>
-  </si>
-  <si>
     <t>60.96</t>
   </si>
   <si>
-    <t>GCA_963817365</t>
-  </si>
-  <si>
     <t>47.18</t>
   </si>
   <si>
-    <t>GCA_963793545</t>
-  </si>
-  <si>
     <t>Decalcified Empetrum dunes, MFD06714.bin.1.228</t>
   </si>
   <si>
@@ -381,9 +363,6 @@
     <t>57.98</t>
   </si>
   <si>
-    <t>GCA_963809115</t>
-  </si>
-  <si>
     <t>Degraded raised bog</t>
   </si>
   <si>
@@ -396,9 +375,6 @@
     <t>Storelung</t>
   </si>
   <si>
-    <t>GCA_963818875</t>
-  </si>
-  <si>
     <t>pratensis</t>
   </si>
   <si>
@@ -436,15 +412,6 @@
   </si>
   <si>
     <t>regalis</t>
-  </si>
-  <si>
-    <t>Names v2</t>
-  </si>
-  <si>
-    <t>Fremeni (Methylocapsa MAG_30, humid!)</t>
-  </si>
-  <si>
-    <t>Caladan()</t>
   </si>
   <si>
     <t xml:space="preserve">scaenica (scae’ni.ca. L. fem. adj. scaenica, scenic, picturesque, referring to the recovery of the species from a scenic location in calcareous environments). </t>
@@ -547,6 +514,33 @@
   </si>
   <si>
     <t xml:space="preserve">#Supplementary Data File 3: Protologue tables </t>
+  </si>
+  <si>
+    <t>GCA_963706215.1</t>
+  </si>
+  <si>
+    <t>GCA_963764725.1</t>
+  </si>
+  <si>
+    <t>GCA_963818875.1</t>
+  </si>
+  <si>
+    <t>GCA_963809115.1</t>
+  </si>
+  <si>
+    <t>GCA_963717565.1</t>
+  </si>
+  <si>
+    <t>GCA_963706255.1</t>
+  </si>
+  <si>
+    <t>GCA_963817365.1</t>
+  </si>
+  <si>
+    <t>GCA_963793545.1</t>
+  </si>
+  <si>
+    <t>0-10 cm</t>
   </si>
 </sst>
 </file>
@@ -976,7 +970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE2AEA78-D811-483B-B3EC-FC7DCA3AB60A}">
-  <dimension ref="A1:AE32"/>
+  <dimension ref="A1:AE31"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="36.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -996,7 +990,7 @@
   <sheetData>
     <row r="1" spans="1:31">
       <c r="A1" s="4" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="6"/>
@@ -1031,13 +1025,13 @@
         <v>55</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>57</v>
@@ -1046,10 +1040,10 @@
         <v>58</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -1066,7 +1060,7 @@
         <v>41</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>61</v>
@@ -1090,7 +1084,7 @@
         <v>63</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -1104,34 +1098,34 @@
         <v>51</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="I4" s="3" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="14.4">
@@ -1148,7 +1142,7 @@
         <v>40</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>64</v>
@@ -1172,7 +1166,7 @@
         <v>66</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="27.6">
@@ -1189,7 +1183,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -1205,40 +1199,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="J7" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="K7" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="L7" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="M7" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1314,31 +1308,31 @@
         <v>86</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>90</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -1355,31 +1349,31 @@
         <v>86</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>90</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -1481,28 +1475,28 @@
         <v>99</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>91</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="J13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="M13" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -1570,7 +1564,7 @@
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="8" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>76</v>
@@ -1608,10 +1602,10 @@
         <v>74</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>77</v>
@@ -1650,10 +1644,10 @@
         <v>72</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>76</v>
@@ -1765,7 +1759,9 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="G20" s="3" t="s">
+        <v>154</v>
+      </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
@@ -2165,10 +2161,10 @@
         <v>73</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>75</v>
@@ -2222,18 +2218,6 @@
       </c>
       <c r="M31" s="5" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="27.6">
-      <c r="A32" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2244,6 +2228,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101008C38B1239D23D3409364AAD8B4557619" ma:contentTypeVersion="39" ma:contentTypeDescription="Opret et nyt dokument." ma:contentTypeScope="" ma:versionID="38ce3dfc9af8bf9c8d2d2e3ddecd1ab4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="91114dac-0c15-4fee-8f62-55e579a5a7ae" xmlns:ns3="1a784baf-302e-4e2f-9973-3679c4e175c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e0a2639dc66920b530c4c995a3c0b6b9" ns2:_="" ns3:_="">
     <xsd:import namespace="91114dac-0c15-4fee-8f62-55e579a5a7ae"/>
@@ -2692,15 +2685,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2758,6 +2742,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAA20521-990D-4B54-B7B4-3181B673C318}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D711C28-D8D5-43AE-BE98-8AAF1A144A96}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2776,20 +2768,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAA20521-990D-4B54-B7B4-3181B673C318}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64D54EB6-0F01-4302-897B-1E6F2BB36FC4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="91114dac-0c15-4fee-8f62-55e579a5a7ae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="91114dac-0c15-4fee-8f62-55e579a5a7ae"/>
     <ds:schemaRef ds:uri="1a784baf-302e-4e2f-9973-3679c4e175c7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
